--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2015/Aircraft_Cumulative_Statistics_2015.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2015/Aircraft_Cumulative_Statistics_2015.xlsx
@@ -13,66 +13,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="39" uniqueCount="39">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -154,10 +175,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -177,40 +198,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
@@ -218,40 +239,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>27757086126</v>
+        <v>3105196353</v>
       </c>
       <c r="C2" s="0">
-        <v>32585279635</v>
+        <v>3884184772</v>
       </c>
       <c r="D2" s="0">
-        <v>782924</v>
+        <v>29213</v>
       </c>
       <c r="E2" s="0">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>142845</v>
+        <v>190008</v>
       </c>
       <c r="G2" s="0">
-        <v>3.4300000000000002</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>11.51</v>
+        <v>2.1600000000000001</v>
       </c>
       <c r="I2" s="0">
-        <v>85.180000000000007</v>
+        <v>79.939999999999998</v>
       </c>
       <c r="J2" s="0">
-        <v>1375</v>
+        <v>409</v>
       </c>
       <c r="K2" s="0">
-        <v>3130</v>
+        <v>900.88999999999999</v>
       </c>
       <c r="L2" s="0">
-        <v>18.890000000000001</v>
+        <v>18.02</v>
       </c>
       <c r="M2" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="3">
@@ -259,40 +280,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>3661391112</v>
+        <v>7229636944</v>
       </c>
       <c r="C3" s="0">
-        <v>4246242104</v>
+        <v>8861661339</v>
       </c>
       <c r="D3" s="0">
-        <v>500736</v>
+        <v>106677</v>
       </c>
       <c r="E3" s="0">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>23490</v>
+        <v>465983</v>
       </c>
       <c r="G3" s="0">
-        <v>2.77</v>
+        <v>5.6100000000000003</v>
       </c>
       <c r="H3" s="0">
-        <v>7.1699999999999999</v>
+        <v>8.1099999999999994</v>
       </c>
       <c r="I3" s="0">
-        <v>86.230000000000004</v>
+        <v>81.579999999999998</v>
       </c>
       <c r="J3" s="0">
-        <v>1021</v>
+        <v>380</v>
       </c>
       <c r="K3" s="0">
-        <v>3278</v>
+        <v>1225.46</v>
       </c>
       <c r="L3" s="0">
-        <v>18.600000000000001</v>
+        <v>24.510000000000002</v>
       </c>
       <c r="M3" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -300,40 +321,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>152565256475</v>
+        <v>993163469</v>
       </c>
       <c r="C4" s="0">
-        <v>183096112728</v>
+        <v>1241527403</v>
       </c>
       <c r="D4" s="0">
-        <v>734883</v>
+        <v>155191</v>
       </c>
       <c r="E4" s="0">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="F4" s="0">
-        <v>729570</v>
+        <v>37686</v>
       </c>
       <c r="G4" s="0">
-        <v>2.9300000000000002</v>
+        <v>4.71</v>
       </c>
       <c r="H4" s="0">
-        <v>10.08</v>
+        <v>8.1799999999999997</v>
       </c>
       <c r="I4" s="0">
-        <v>83.329999999999998</v>
+        <v>80</v>
       </c>
       <c r="J4" s="0">
-        <v>1391</v>
+        <v>477</v>
       </c>
       <c r="K4" s="0">
-        <v>4645</v>
+        <v>1323.9100000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>26.350000000000001</v>
+        <v>19.16</v>
       </c>
       <c r="M4" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="5">
@@ -341,40 +362,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>153318931099</v>
+        <v>8821962999</v>
       </c>
       <c r="C5" s="0">
-        <v>179343307582</v>
+        <v>10738008651</v>
       </c>
       <c r="D5" s="0">
-        <v>823507</v>
+        <v>261075</v>
       </c>
       <c r="E5" s="0">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="F5" s="0">
-        <v>708298</v>
+        <v>238556</v>
       </c>
       <c r="G5" s="0">
-        <v>3.25</v>
+        <v>5.7999999999999998</v>
       </c>
       <c r="H5" s="0">
-        <v>10.630000000000001</v>
+        <v>11.210000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>85.489999999999995</v>
+        <v>82.159999999999997</v>
       </c>
       <c r="J5" s="0">
-        <v>1336</v>
+        <v>583</v>
       </c>
       <c r="K5" s="0">
-        <v>4799</v>
+        <v>1324.5999999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>26.170000000000002</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="6">
@@ -382,40 +403,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>13395144551</v>
+        <v>12217442353</v>
       </c>
       <c r="C6" s="0">
-        <v>15495494516</v>
+        <v>15103199234</v>
       </c>
       <c r="D6" s="0">
-        <v>743189</v>
+        <v>123493</v>
       </c>
       <c r="E6" s="0">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="F6" s="0">
-        <v>97391</v>
+        <v>389750</v>
       </c>
       <c r="G6" s="0">
-        <v>4.6699999999999999</v>
+        <v>3.1899999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>12.390000000000001</v>
+        <v>5.8499999999999996</v>
       </c>
       <c r="I6" s="0">
-        <v>86.450000000000003</v>
+        <v>80.890000000000001</v>
       </c>
       <c r="J6" s="0">
-        <v>1006</v>
+        <v>567</v>
       </c>
       <c r="K6" s="0">
-        <v>3325</v>
+        <v>1179.03</v>
       </c>
       <c r="L6" s="0">
-        <v>21.050000000000001</v>
+        <v>17.27</v>
       </c>
       <c r="M6" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -423,40 +444,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>14409425975</v>
+        <v>6389377574</v>
       </c>
       <c r="C7" s="0">
-        <v>17691799147</v>
+        <v>7778705685</v>
       </c>
       <c r="D7" s="0">
-        <v>1004645</v>
+        <v>291228</v>
       </c>
       <c r="E7" s="0">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="F7" s="0">
-        <v>80595</v>
+        <v>135498</v>
       </c>
       <c r="G7" s="0">
-        <v>4.5800000000000001</v>
+        <v>5.0700000000000003</v>
       </c>
       <c r="H7" s="0">
-        <v>9.5999999999999996</v>
+        <v>9.3200000000000003</v>
       </c>
       <c r="I7" s="0">
-        <v>81.450000000000003</v>
+        <v>82.140000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>826</v>
+        <v>574</v>
       </c>
       <c r="K7" s="0">
-        <v>6194</v>
+        <v>3025.8299999999999</v>
       </c>
       <c r="L7" s="0">
-        <v>25.359999999999999</v>
+        <v>30.280000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -464,40 +485,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>41749713632</v>
+        <v>13450662047</v>
       </c>
       <c r="C8" s="0">
-        <v>49345813023</v>
+        <v>16367393668</v>
       </c>
       <c r="D8" s="0">
-        <v>650057</v>
+        <v>221540</v>
       </c>
       <c r="E8" s="0">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="F8" s="0">
-        <v>317755</v>
+        <v>382479</v>
       </c>
       <c r="G8" s="0">
-        <v>4.1900000000000004</v>
+        <v>5.1799999999999997</v>
       </c>
       <c r="H8" s="0">
-        <v>11.890000000000001</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="I8" s="0">
-        <v>84.609999999999999</v>
+        <v>82.180000000000007</v>
       </c>
       <c r="J8" s="0">
-        <v>1092</v>
+        <v>559</v>
       </c>
       <c r="K8" s="0">
-        <v>3402</v>
+        <v>937.13</v>
       </c>
       <c r="L8" s="0">
-        <v>24.289999999999999</v>
+        <v>12.25</v>
       </c>
       <c r="M8" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.040000000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -505,40 +526,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>102201768436</v>
+        <v>36892735556</v>
       </c>
       <c r="C9" s="0">
-        <v>121458889567</v>
+        <v>43803867145</v>
       </c>
       <c r="D9" s="0">
-        <v>614173</v>
+        <v>460657</v>
       </c>
       <c r="E9" s="0">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="F9" s="0">
-        <v>1017220</v>
+        <v>384278</v>
       </c>
       <c r="G9" s="0">
-        <v>5.1399999999999997</v>
+        <v>4.04</v>
       </c>
       <c r="H9" s="0">
-        <v>10.99</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="I9" s="0">
-        <v>84.150000000000006</v>
+        <v>84.219999999999999</v>
       </c>
       <c r="J9" s="0">
-        <v>800</v>
+        <v>856</v>
       </c>
       <c r="K9" s="0">
-        <v>3272</v>
+        <v>3385.3699999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>21.98</v>
+        <v>25.48</v>
       </c>
       <c r="M9" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="10">
@@ -546,40 +567,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>17995600312</v>
+        <v>82383476634</v>
       </c>
       <c r="C10" s="0">
-        <v>21350418935</v>
+        <v>96545208328</v>
       </c>
       <c r="D10" s="0">
-        <v>804765</v>
+        <v>669523</v>
       </c>
       <c r="E10" s="0">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="F10" s="0">
-        <v>128139</v>
+        <v>559943</v>
       </c>
       <c r="G10" s="0">
-        <v>4.8300000000000001</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>12.65</v>
+        <v>11.09</v>
       </c>
       <c r="I10" s="0">
-        <v>84.290000000000006</v>
+        <v>85.329999999999998</v>
       </c>
       <c r="J10" s="0">
-        <v>993</v>
+        <v>1108</v>
       </c>
       <c r="K10" s="0">
-        <v>3145</v>
+        <v>3633.5999999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>18.739999999999998</v>
+        <v>23.34</v>
       </c>
       <c r="M10" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.059999999999999998</v>
       </c>
     </row>
     <row r="11">
@@ -587,40 +608,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>3296058115</v>
+        <v>29544148200</v>
       </c>
       <c r="C11" s="0">
-        <v>4129110201</v>
+        <v>33861613046</v>
       </c>
       <c r="D11" s="0">
-        <v>540459</v>
+        <v>751145</v>
       </c>
       <c r="E11" s="0">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="F11" s="0">
-        <v>23273</v>
+        <v>143652</v>
       </c>
       <c r="G11" s="0">
-        <v>3.0499999999999998</v>
+        <v>3.1899999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>8.9600000000000009</v>
+        <v>10.970000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>79.819999999999993</v>
+        <v>87.25</v>
       </c>
       <c r="J11" s="0">
-        <v>1173</v>
+        <v>1373</v>
       </c>
       <c r="K11" s="0">
-        <v>4379</v>
+        <v>3769.79</v>
       </c>
       <c r="L11" s="0">
-        <v>28.969999999999999</v>
+        <v>21.800000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="12">
@@ -628,40 +649,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>168903103093</v>
+        <v>6987218327</v>
       </c>
       <c r="C12" s="0">
-        <v>201876896492</v>
+        <v>8424621080</v>
       </c>
       <c r="D12" s="0">
-        <v>806572</v>
+        <v>258424</v>
       </c>
       <c r="E12" s="0">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="F12" s="0">
-        <v>668078</v>
+        <v>192920</v>
       </c>
       <c r="G12" s="0">
-        <v>2.6699999999999999</v>
+        <v>5.9199999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>10.33</v>
+        <v>8.1500000000000004</v>
       </c>
       <c r="I12" s="0">
-        <v>83.670000000000002</v>
+        <v>82.939999999999998</v>
       </c>
       <c r="J12" s="0">
-        <v>1641</v>
+        <v>391</v>
       </c>
       <c r="K12" s="0">
-        <v>4935</v>
+        <v>3413.9000000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>27.43</v>
+        <v>30.370000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="13">
@@ -669,40 +690,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>5531612052</v>
+        <v>86445184147</v>
       </c>
       <c r="C13" s="0">
-        <v>6872367711</v>
+        <v>103998707085</v>
       </c>
       <c r="D13" s="0">
-        <v>155378</v>
+        <v>553096</v>
       </c>
       <c r="E13" s="0">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="F13" s="0">
-        <v>188120</v>
+        <v>951585</v>
       </c>
       <c r="G13" s="0">
-        <v>4.25</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="H13" s="0">
-        <v>7.4400000000000004</v>
+        <v>10.640000000000001</v>
       </c>
       <c r="I13" s="0">
-        <v>80.489999999999995</v>
+        <v>83.120000000000005</v>
       </c>
       <c r="J13" s="0">
-        <v>515</v>
+        <v>778</v>
       </c>
       <c r="K13" s="0">
-        <v>947</v>
+        <v>3367.6700000000001</v>
       </c>
       <c r="L13" s="0">
-        <v>13.5</v>
+        <v>23.969999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -710,40 +731,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>4875597092</v>
+        <v>134633109374</v>
       </c>
       <c r="C14" s="0">
-        <v>6163111129</v>
+        <v>157905146850</v>
       </c>
       <c r="D14" s="0">
-        <v>32535</v>
+        <v>687261</v>
       </c>
       <c r="E14" s="0">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="F14" s="0">
-        <v>261611</v>
+        <v>791519</v>
       </c>
       <c r="G14" s="0">
-        <v>1.3799999999999999</v>
+        <v>3.4399999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>2.1699999999999999</v>
+        <v>10.699999999999999</v>
       </c>
       <c r="I14" s="0">
-        <v>79.109999999999999</v>
+        <v>85.260000000000005</v>
       </c>
       <c r="J14" s="0">
-        <v>433</v>
+        <v>1231</v>
       </c>
       <c r="K14" s="0">
-        <v>897</v>
+        <v>3703.23</v>
       </c>
       <c r="L14" s="0">
-        <v>16.550000000000001</v>
+        <v>22.859999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="15">
@@ -751,40 +772,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>2446560695</v>
+        <v>39369944814</v>
       </c>
       <c r="C15" s="0">
-        <v>3091279096</v>
+        <v>45423124151</v>
       </c>
       <c r="D15" s="0">
-        <v>169385</v>
+        <v>796757</v>
       </c>
       <c r="E15" s="0">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="F15" s="0">
-        <v>80533</v>
+        <v>193384</v>
       </c>
       <c r="G15" s="0">
-        <v>4.4100000000000001</v>
+        <v>3.3900000000000001</v>
       </c>
       <c r="H15" s="0">
-        <v>8.3200000000000003</v>
+        <v>11.289999999999999</v>
       </c>
       <c r="I15" s="0">
-        <v>79.140000000000001</v>
+        <v>86.670000000000002</v>
       </c>
       <c r="J15" s="0">
-        <v>546</v>
+        <v>1350</v>
       </c>
       <c r="K15" s="0">
-        <v>1051</v>
+        <v>3676.9899999999998</v>
       </c>
       <c r="L15" s="0">
-        <v>14.949999999999999</v>
+        <v>21.140000000000001</v>
       </c>
       <c r="M15" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="16">
@@ -792,40 +813,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>6412425337</v>
+        <v>15459918486</v>
       </c>
       <c r="C16" s="0">
-        <v>7814759105</v>
+        <v>17402963694</v>
       </c>
       <c r="D16" s="0">
-        <v>233416</v>
+        <v>843985</v>
       </c>
       <c r="E16" s="0">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="F16" s="0">
-        <v>183928</v>
+        <v>70366</v>
       </c>
       <c r="G16" s="0">
-        <v>5.4900000000000002</v>
+        <v>3.4100000000000001</v>
       </c>
       <c r="H16" s="0">
-        <v>9.7599999999999998</v>
+        <v>11.380000000000001</v>
       </c>
       <c r="I16" s="0">
-        <v>82.060000000000002</v>
+        <v>88.829999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>557</v>
+        <v>1372</v>
       </c>
       <c r="K16" s="0">
-        <v>941</v>
+        <v>3828.27</v>
       </c>
       <c r="L16" s="0">
-        <v>12.359999999999999</v>
+        <v>21.239999999999998</v>
       </c>
       <c r="M16" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="17">
@@ -833,40 +854,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>3516753213</v>
+        <v>59271147654</v>
       </c>
       <c r="C17" s="0">
-        <v>4251919578</v>
+        <v>68999392406</v>
       </c>
       <c r="D17" s="0">
-        <v>135714</v>
+        <v>722204</v>
       </c>
       <c r="E17" s="0">
-        <v>62</v>
+        <v>178</v>
       </c>
       <c r="F17" s="0">
-        <v>177941</v>
+        <v>247645</v>
       </c>
       <c r="G17" s="0">
-        <v>5.6799999999999997</v>
+        <v>2.5899999999999999</v>
       </c>
       <c r="H17" s="0">
-        <v>8.2699999999999996</v>
+        <v>9.8200000000000003</v>
       </c>
       <c r="I17" s="0">
-        <v>82.709999999999994</v>
+        <v>85.900000000000006</v>
       </c>
       <c r="J17" s="0">
-        <v>379</v>
+        <v>1584</v>
       </c>
       <c r="K17" s="0">
-        <v>1355</v>
+        <v>4609.3400000000001</v>
       </c>
       <c r="L17" s="0">
-        <v>21.579999999999998</v>
+        <v>26.149999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="18">
@@ -874,40 +895,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>6199929597</v>
+        <v>11309401910</v>
       </c>
       <c r="C18" s="0">
-        <v>7765795827</v>
+        <v>13093772151</v>
       </c>
       <c r="D18" s="0">
-        <v>190478</v>
+        <v>974964</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>224</v>
       </c>
       <c r="F18" s="0">
-        <v>202030</v>
+        <v>35009</v>
       </c>
       <c r="G18" s="0">
-        <v>4.96</v>
+        <v>2.6099999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>8.8399999999999999</v>
+        <v>10.24</v>
       </c>
       <c r="I18" s="0">
-        <v>79.840000000000003</v>
+        <v>86.370000000000005</v>
       </c>
       <c r="J18" s="0">
-        <v>503</v>
+        <v>1683</v>
       </c>
       <c r="K18" s="0">
-        <v>1348</v>
+        <v>4817.1000000000004</v>
       </c>
       <c r="L18" s="0">
-        <v>17.640000000000001</v>
+        <v>21.640000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.050999999999999997</v>
       </c>
     </row>
     <row r="19">
@@ -915,40 +936,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>16937315277</v>
+        <v>53549869999</v>
       </c>
       <c r="C19" s="0">
-        <v>20373137333</v>
+        <v>66537891945</v>
       </c>
       <c r="D19" s="0">
-        <v>194067</v>
+        <v>1063245</v>
       </c>
       <c r="E19" s="0">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="F19" s="0">
-        <v>612392</v>
+        <v>95258</v>
       </c>
       <c r="G19" s="0">
-        <v>5.8300000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="H19" s="0">
-        <v>10.17</v>
+        <v>10.609999999999999</v>
       </c>
       <c r="I19" s="0">
-        <v>83.140000000000001</v>
+        <v>80.480000000000004</v>
       </c>
       <c r="J19" s="0">
-        <v>527</v>
+        <v>3245</v>
       </c>
       <c r="K19" s="0">
-        <v>1220</v>
+        <v>6242.0699999999997</v>
       </c>
       <c r="L19" s="0">
-        <v>19.690000000000001</v>
+        <v>28.940000000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="20">
@@ -956,40 +977,327 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
+        <v>16043204405</v>
+      </c>
+      <c r="C20" s="0">
+        <v>19821432301</v>
+      </c>
+      <c r="D20" s="0">
+        <v>1477007</v>
+      </c>
+      <c r="E20" s="0">
+        <v>244</v>
+      </c>
+      <c r="F20" s="0">
+        <v>20070</v>
+      </c>
+      <c r="G20" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="0">
+        <v>12.609999999999999</v>
+      </c>
+      <c r="I20" s="0">
+        <v>80.939999999999998</v>
+      </c>
+      <c r="J20" s="0">
+        <v>4051</v>
+      </c>
+      <c r="K20" s="0">
+        <v>6216.2399999999998</v>
+      </c>
+      <c r="L20" s="0">
+        <v>25.5</v>
+      </c>
+      <c r="M20" s="0">
+        <v>0.052999999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0">
+        <v>18561922198</v>
+      </c>
+      <c r="C21" s="0">
+        <v>22838954562</v>
+      </c>
+      <c r="D21" s="0">
+        <v>1602734</v>
+      </c>
+      <c r="E21" s="0">
+        <v>275</v>
+      </c>
+      <c r="F21" s="0">
+        <v>22835</v>
+      </c>
+      <c r="G21" s="0">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="H21" s="0">
+        <v>12.529999999999999</v>
+      </c>
+      <c r="I21" s="0">
+        <v>81.269999999999996</v>
+      </c>
+      <c r="J21" s="0">
+        <v>3707</v>
+      </c>
+      <c r="K21" s="0">
+        <v>6836.5100000000002</v>
+      </c>
+      <c r="L21" s="0">
+        <v>25.289999999999999</v>
+      </c>
+      <c r="M21" s="0">
+        <v>0.052999999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="0">
+        <v>15574698070</v>
+      </c>
+      <c r="C22" s="0">
+        <v>18405311476</v>
+      </c>
+      <c r="D22" s="0">
+        <v>1862886</v>
+      </c>
+      <c r="E22" s="0">
+        <v>291</v>
+      </c>
+      <c r="F22" s="0">
+        <v>15422</v>
+      </c>
+      <c r="G22" s="0">
+        <v>1.5600000000000001</v>
+      </c>
+      <c r="H22" s="0">
+        <v>13.32</v>
+      </c>
+      <c r="I22" s="0">
+        <v>84.620000000000005</v>
+      </c>
+      <c r="J22" s="0">
+        <v>4099</v>
+      </c>
+      <c r="K22" s="0">
+        <v>6992.04</v>
+      </c>
+      <c r="L22" s="0">
+        <v>24.010000000000002</v>
+      </c>
+      <c r="M22" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="0">
+        <v>7106195969</v>
+      </c>
+      <c r="C23" s="0">
+        <v>8837173441</v>
+      </c>
+      <c r="D23" s="0">
+        <v>1328898</v>
+      </c>
+      <c r="E23" s="0">
+        <v>221</v>
+      </c>
+      <c r="F23" s="0">
+        <v>8681</v>
+      </c>
+      <c r="G23" s="0">
+        <v>1.3100000000000001</v>
+      </c>
+      <c r="H23" s="0">
+        <v>12</v>
+      </c>
+      <c r="I23" s="0">
+        <v>80.409999999999997</v>
+      </c>
+      <c r="J23" s="0">
+        <v>4612</v>
+      </c>
+      <c r="K23" s="0">
+        <v>6416.8199999999997</v>
+      </c>
+      <c r="L23" s="0">
+        <v>29.07</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0.058000000000000003</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>3524943561</v>
+      </c>
+      <c r="C24" s="0">
+        <v>4190482296</v>
+      </c>
+      <c r="D24" s="0">
+        <v>1575369</v>
+      </c>
+      <c r="E24" s="0">
+        <v>252</v>
+      </c>
+      <c r="F24" s="0">
+        <v>3180</v>
+      </c>
+      <c r="G24" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="H24" s="0">
+        <v>12.18</v>
+      </c>
+      <c r="I24" s="0">
+        <v>84.120000000000005</v>
+      </c>
+      <c r="J24" s="0">
+        <v>5229</v>
+      </c>
+      <c r="K24" s="0">
+        <v>6779.7200000000003</v>
+      </c>
+      <c r="L24" s="0">
+        <v>26.899999999999999</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.051999999999999998</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>66432438526</v>
+      </c>
+      <c r="C25" s="0">
+        <v>80424179428</v>
+      </c>
+      <c r="D25" s="0">
+        <v>1582530</v>
+      </c>
+      <c r="E25" s="0">
+        <v>271</v>
+      </c>
+      <c r="F25" s="0">
+        <v>58878</v>
+      </c>
+      <c r="G25" s="0">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>11.720000000000001</v>
+      </c>
+      <c r="I25" s="0">
+        <v>82.599999999999994</v>
+      </c>
+      <c r="J25" s="0">
+        <v>5079</v>
+      </c>
+      <c r="K25" s="0">
+        <v>8840.6100000000006</v>
+      </c>
+      <c r="L25" s="0">
+        <v>32.869999999999997</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.065000000000000002</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>9876672620</v>
+      </c>
+      <c r="C26" s="0">
+        <v>12463211572</v>
+      </c>
+      <c r="D26" s="0">
+        <v>1941310</v>
+      </c>
+      <c r="E26" s="0">
+        <v>310</v>
+      </c>
+      <c r="F26" s="0">
+        <v>8624</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1.3400000000000001</v>
+      </c>
+      <c r="H26" s="0">
+        <v>12.640000000000001</v>
+      </c>
+      <c r="I26" s="0">
+        <v>79.25</v>
+      </c>
+      <c r="J26" s="0">
+        <v>4664</v>
+      </c>
+      <c r="K26" s="0">
+        <v>10326.940000000001</v>
+      </c>
+      <c r="L26" s="0">
+        <v>33.32</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
         <v>745173672189</v>
       </c>
-      <c r="C20" s="0">
+      <c r="C27" s="0">
         <v>886951733709</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D27" s="0">
         <v>562754</v>
       </c>
-      <c r="E20" s="0">
+      <c r="E27" s="0">
         <v>129</v>
       </c>
-      <c r="F20" s="0">
+      <c r="F27" s="0">
         <v>5643209</v>
       </c>
-      <c r="G20" s="0">
+      <c r="G27" s="0">
         <v>3.5800000000000001</v>
       </c>
-      <c r="H20" s="0">
+      <c r="H27" s="0">
         <v>9.3699999999999992</v>
       </c>
-      <c r="I20" s="0">
+      <c r="I27" s="0">
         <v>84.019999999999996</v>
       </c>
-      <c r="J20" s="0">
+      <c r="J27" s="0">
         <v>993</v>
       </c>
-      <c r="K20" s="0">
-        <v>3655</v>
-      </c>
-      <c r="L20" s="0">
+      <c r="K27" s="0">
+        <v>3654.79</v>
+      </c>
+      <c r="L27" s="0">
         <v>24.390000000000001</v>
       </c>
-      <c r="M20" s="0">
-        <v>0.059999999999999998</v>
+      <c r="M27" s="0">
+        <v>0.060999999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2015/Aircraft_Cumulative_Statistics_2015.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2015/Aircraft_Cumulative_Statistics_2015.xlsx
@@ -13,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,6 +33,18 @@
     <t>E175</t>
   </si>
   <si>
+    <t>Q100</t>
+  </si>
+  <si>
+    <t>Q200</t>
+  </si>
+  <si>
+    <t>Q300</t>
+  </si>
+  <si>
+    <t>Q400</t>
+  </si>
+  <si>
     <t>CRJ-700</t>
   </si>
   <si>
@@ -48,7 +63,22 @@
     <t>A321</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
     <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-300</t>
+  </si>
+  <si>
+    <t>B737-400</t>
+  </si>
+  <si>
+    <t>B737-500</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -175,7 +205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -198,40 +228,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -239,40 +269,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>3105196353</v>
+        <v>518763525</v>
       </c>
       <c r="C2" s="0">
-        <v>3884184772</v>
+        <v>692217856</v>
       </c>
       <c r="D2" s="0">
-        <v>29213</v>
+        <v>24503</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F2" s="0">
-        <v>190008</v>
+        <v>40217</v>
       </c>
       <c r="G2" s="0">
-        <v>1.4299999999999999</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="H2" s="0">
         <v>2.1600000000000001</v>
       </c>
       <c r="I2" s="0">
-        <v>79.939999999999998</v>
+        <v>74.939999999999998</v>
       </c>
       <c r="J2" s="0">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="K2" s="0">
-        <v>900.88999999999999</v>
+        <v>896.55999999999995</v>
       </c>
       <c r="L2" s="0">
-        <v>18.02</v>
+        <v>20.379999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -280,40 +310,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>7229636944</v>
+        <v>3105196353</v>
       </c>
       <c r="C3" s="0">
-        <v>8861661339</v>
+        <v>3884184772</v>
       </c>
       <c r="D3" s="0">
-        <v>106677</v>
+        <v>29213</v>
       </c>
       <c r="E3" s="0">
         <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>465983</v>
+        <v>190008</v>
       </c>
       <c r="G3" s="0">
-        <v>5.6100000000000003</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>8.1099999999999994</v>
+        <v>2.1600000000000001</v>
       </c>
       <c r="I3" s="0">
-        <v>81.579999999999998</v>
+        <v>79.939999999999998</v>
       </c>
       <c r="J3" s="0">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="K3" s="0">
-        <v>1225.46</v>
+        <v>900.88999999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>24.510000000000002</v>
+        <v>18.02</v>
       </c>
       <c r="M3" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="4">
@@ -321,40 +351,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>993163469</v>
+        <v>7229636944</v>
       </c>
       <c r="C4" s="0">
-        <v>1241527403</v>
+        <v>8861661339</v>
       </c>
       <c r="D4" s="0">
-        <v>155191</v>
+        <v>106677</v>
       </c>
       <c r="E4" s="0">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F4" s="0">
-        <v>37686</v>
+        <v>465983</v>
       </c>
       <c r="G4" s="0">
-        <v>4.71</v>
+        <v>5.6100000000000003</v>
       </c>
       <c r="H4" s="0">
-        <v>8.1799999999999997</v>
+        <v>8.1099999999999994</v>
       </c>
       <c r="I4" s="0">
-        <v>80</v>
+        <v>81.579999999999998</v>
       </c>
       <c r="J4" s="0">
-        <v>477</v>
+        <v>380</v>
       </c>
       <c r="K4" s="0">
-        <v>1323.9100000000001</v>
+        <v>1225.46</v>
       </c>
       <c r="L4" s="0">
-        <v>19.16</v>
+        <v>24.510000000000002</v>
       </c>
       <c r="M4" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -362,40 +392,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>8821962999</v>
+        <v>993163469</v>
       </c>
       <c r="C5" s="0">
-        <v>10738008651</v>
+        <v>1241527403</v>
       </c>
       <c r="D5" s="0">
-        <v>261075</v>
+        <v>155191</v>
       </c>
       <c r="E5" s="0">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F5" s="0">
-        <v>238556</v>
+        <v>37686</v>
       </c>
       <c r="G5" s="0">
-        <v>5.7999999999999998</v>
+        <v>4.71</v>
       </c>
       <c r="H5" s="0">
-        <v>11.210000000000001</v>
+        <v>8.1799999999999997</v>
       </c>
       <c r="I5" s="0">
-        <v>82.159999999999997</v>
+        <v>80</v>
       </c>
       <c r="J5" s="0">
-        <v>583</v>
+        <v>477</v>
       </c>
       <c r="K5" s="0">
-        <v>1324.5999999999999</v>
+        <v>1323.9100000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>17.149999999999999</v>
+        <v>19.16</v>
       </c>
       <c r="M5" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="6">
@@ -403,40 +433,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>12217442353</v>
+        <v>8821962999</v>
       </c>
       <c r="C6" s="0">
-        <v>15103199234</v>
+        <v>10738008651</v>
       </c>
       <c r="D6" s="0">
-        <v>123493</v>
+        <v>261075</v>
       </c>
       <c r="E6" s="0">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F6" s="0">
-        <v>389750</v>
+        <v>238556</v>
       </c>
       <c r="G6" s="0">
-        <v>3.1899999999999999</v>
+        <v>5.7999999999999998</v>
       </c>
       <c r="H6" s="0">
-        <v>5.8499999999999996</v>
+        <v>11.210000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>80.890000000000001</v>
+        <v>82.159999999999997</v>
       </c>
       <c r="J6" s="0">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="K6" s="0">
-        <v>1179.03</v>
+        <v>1324.5999999999999</v>
       </c>
       <c r="L6" s="0">
-        <v>17.27</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="7">
@@ -444,40 +474,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>6389377574</v>
+        <v>279080901</v>
       </c>
       <c r="C7" s="0">
-        <v>7778705685</v>
+        <v>375150078</v>
       </c>
       <c r="D7" s="0">
-        <v>291228</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="F7" s="0">
-        <v>135498</v>
+        <v>61513</v>
       </c>
       <c r="G7" s="0">
-        <v>5.0700000000000003</v>
+        <v>0</v>
       </c>
       <c r="H7" s="0">
-        <v>9.3200000000000003</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0">
-        <v>82.140000000000001</v>
+        <v>74.390000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>574</v>
+        <v>169</v>
       </c>
       <c r="K7" s="0">
-        <v>3025.8299999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0">
-        <v>30.280000000000001</v>
+        <v>0</v>
       </c>
       <c r="M7" s="0">
-        <v>0.097000000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -485,40 +515,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>13450662047</v>
+        <v>139684827</v>
       </c>
       <c r="C8" s="0">
-        <v>16367393668</v>
+        <v>175752997</v>
       </c>
       <c r="D8" s="0">
-        <v>221540</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="F8" s="0">
-        <v>382479</v>
+        <v>24670</v>
       </c>
       <c r="G8" s="0">
-        <v>5.1799999999999997</v>
+        <v>0</v>
       </c>
       <c r="H8" s="0">
-        <v>9.4399999999999995</v>
+        <v>0</v>
       </c>
       <c r="I8" s="0">
-        <v>82.180000000000007</v>
+        <v>79.480000000000004</v>
       </c>
       <c r="J8" s="0">
-        <v>559</v>
+        <v>193</v>
       </c>
       <c r="K8" s="0">
-        <v>937.13</v>
+        <v>0</v>
       </c>
       <c r="L8" s="0">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="M8" s="0">
-        <v>0.040000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -526,40 +556,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>36892735556</v>
+        <v>286152561</v>
       </c>
       <c r="C9" s="0">
-        <v>43803867145</v>
+        <v>353492343</v>
       </c>
       <c r="D9" s="0">
-        <v>460657</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="F9" s="0">
-        <v>384278</v>
+        <v>39825</v>
       </c>
       <c r="G9" s="0">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="H9" s="0">
-        <v>9.5399999999999991</v>
+        <v>0</v>
       </c>
       <c r="I9" s="0">
-        <v>84.219999999999999</v>
+        <v>80.950000000000003</v>
       </c>
       <c r="J9" s="0">
-        <v>856</v>
+        <v>178</v>
       </c>
       <c r="K9" s="0">
-        <v>3385.3699999999999</v>
+        <v>0</v>
       </c>
       <c r="L9" s="0">
-        <v>25.48</v>
+        <v>0</v>
       </c>
       <c r="M9" s="0">
-        <v>0.070000000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -567,40 +597,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>82383476634</v>
+        <v>2886651167</v>
       </c>
       <c r="C10" s="0">
-        <v>96545208328</v>
+        <v>3622728601</v>
       </c>
       <c r="D10" s="0">
-        <v>669523</v>
+        <v>135886</v>
       </c>
       <c r="E10" s="0">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="F10" s="0">
-        <v>559943</v>
+        <v>168737</v>
       </c>
       <c r="G10" s="0">
-        <v>3.8799999999999999</v>
+        <v>6.3300000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>11.09</v>
+        <v>7.6799999999999997</v>
       </c>
       <c r="I10" s="0">
-        <v>85.329999999999998</v>
+        <v>79.680000000000007</v>
       </c>
       <c r="J10" s="0">
-        <v>1108</v>
+        <v>287</v>
       </c>
       <c r="K10" s="0">
-        <v>3633.5999999999999</v>
+        <v>1443.5</v>
       </c>
       <c r="L10" s="0">
-        <v>23.34</v>
+        <v>19.300000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="11">
@@ -608,40 +638,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>29544148200</v>
+        <v>12217442353</v>
       </c>
       <c r="C11" s="0">
-        <v>33861613046</v>
+        <v>15103199234</v>
       </c>
       <c r="D11" s="0">
-        <v>751145</v>
+        <v>123493</v>
       </c>
       <c r="E11" s="0">
-        <v>179</v>
+        <v>68</v>
       </c>
       <c r="F11" s="0">
-        <v>143652</v>
+        <v>389750</v>
       </c>
       <c r="G11" s="0">
         <v>3.1899999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>10.970000000000001</v>
+        <v>5.8499999999999996</v>
       </c>
       <c r="I11" s="0">
-        <v>87.25</v>
+        <v>80.890000000000001</v>
       </c>
       <c r="J11" s="0">
-        <v>1373</v>
+        <v>567</v>
       </c>
       <c r="K11" s="0">
-        <v>3769.79</v>
+        <v>1179.03</v>
       </c>
       <c r="L11" s="0">
-        <v>21.800000000000001</v>
+        <v>17.27</v>
       </c>
       <c r="M11" s="0">
-        <v>0.055</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -649,40 +679,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>6987218327</v>
+        <v>6389377574</v>
       </c>
       <c r="C12" s="0">
-        <v>8424621080</v>
+        <v>7778705685</v>
       </c>
       <c r="D12" s="0">
-        <v>258424</v>
+        <v>291228</v>
       </c>
       <c r="E12" s="0">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F12" s="0">
-        <v>192920</v>
+        <v>135498</v>
       </c>
       <c r="G12" s="0">
-        <v>5.9199999999999999</v>
+        <v>5.0700000000000003</v>
       </c>
       <c r="H12" s="0">
-        <v>8.1500000000000004</v>
+        <v>9.3200000000000003</v>
       </c>
       <c r="I12" s="0">
-        <v>82.939999999999998</v>
+        <v>82.140000000000001</v>
       </c>
       <c r="J12" s="0">
-        <v>391</v>
+        <v>574</v>
       </c>
       <c r="K12" s="0">
-        <v>3413.9000000000001</v>
+        <v>3025.8299999999999</v>
       </c>
       <c r="L12" s="0">
-        <v>30.370000000000001</v>
+        <v>30.280000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.108</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="13">
@@ -690,40 +720,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>86445184147</v>
+        <v>13450662047</v>
       </c>
       <c r="C13" s="0">
-        <v>103998707085</v>
+        <v>16367393668</v>
       </c>
       <c r="D13" s="0">
-        <v>553096</v>
+        <v>221540</v>
       </c>
       <c r="E13" s="0">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="F13" s="0">
-        <v>951585</v>
+        <v>382479</v>
       </c>
       <c r="G13" s="0">
-        <v>5.0599999999999996</v>
+        <v>5.1799999999999997</v>
       </c>
       <c r="H13" s="0">
-        <v>10.640000000000001</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="I13" s="0">
-        <v>83.120000000000005</v>
+        <v>82.180000000000007</v>
       </c>
       <c r="J13" s="0">
-        <v>778</v>
+        <v>559</v>
       </c>
       <c r="K13" s="0">
-        <v>3367.6700000000001</v>
+        <v>937.13</v>
       </c>
       <c r="L13" s="0">
-        <v>23.969999999999999</v>
+        <v>12.25</v>
       </c>
       <c r="M13" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.040000000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -731,40 +761,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>134633109374</v>
+        <v>36892735556</v>
       </c>
       <c r="C14" s="0">
-        <v>157905146850</v>
+        <v>43803867145</v>
       </c>
       <c r="D14" s="0">
-        <v>687261</v>
+        <v>460657</v>
       </c>
       <c r="E14" s="0">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="F14" s="0">
-        <v>791519</v>
+        <v>384278</v>
       </c>
       <c r="G14" s="0">
-        <v>3.4399999999999999</v>
+        <v>4.04</v>
       </c>
       <c r="H14" s="0">
-        <v>10.699999999999999</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="I14" s="0">
-        <v>85.260000000000005</v>
+        <v>84.219999999999999</v>
       </c>
       <c r="J14" s="0">
-        <v>1231</v>
+        <v>856</v>
       </c>
       <c r="K14" s="0">
-        <v>3703.23</v>
+        <v>3385.3699999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>22.859999999999999</v>
+        <v>25.48</v>
       </c>
       <c r="M14" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="15">
@@ -772,40 +802,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>39369944814</v>
+        <v>82383476634</v>
       </c>
       <c r="C15" s="0">
-        <v>45423124151</v>
+        <v>96545208328</v>
       </c>
       <c r="D15" s="0">
-        <v>796757</v>
+        <v>669523</v>
       </c>
       <c r="E15" s="0">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="F15" s="0">
-        <v>193384</v>
+        <v>559943</v>
       </c>
       <c r="G15" s="0">
-        <v>3.3900000000000001</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>11.289999999999999</v>
+        <v>11.09</v>
       </c>
       <c r="I15" s="0">
-        <v>86.670000000000002</v>
+        <v>85.329999999999998</v>
       </c>
       <c r="J15" s="0">
-        <v>1350</v>
+        <v>1108</v>
       </c>
       <c r="K15" s="0">
-        <v>3676.9899999999998</v>
+        <v>3633.5999999999999</v>
       </c>
       <c r="L15" s="0">
-        <v>21.140000000000001</v>
+        <v>23.34</v>
       </c>
       <c r="M15" s="0">
-        <v>0.051999999999999998</v>
+        <v>0.059999999999999998</v>
       </c>
     </row>
     <row r="16">
@@ -813,40 +843,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>15459918486</v>
+        <v>29544148200</v>
       </c>
       <c r="C16" s="0">
-        <v>17402963694</v>
+        <v>33861613046</v>
       </c>
       <c r="D16" s="0">
-        <v>843985</v>
+        <v>751145</v>
       </c>
       <c r="E16" s="0">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F16" s="0">
-        <v>70366</v>
+        <v>143652</v>
       </c>
       <c r="G16" s="0">
-        <v>3.4100000000000001</v>
+        <v>3.1899999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>11.380000000000001</v>
+        <v>10.970000000000001</v>
       </c>
       <c r="I16" s="0">
-        <v>88.829999999999998</v>
+        <v>87.25</v>
       </c>
       <c r="J16" s="0">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="K16" s="0">
-        <v>3828.27</v>
+        <v>3769.79</v>
       </c>
       <c r="L16" s="0">
-        <v>21.239999999999998</v>
+        <v>21.800000000000001</v>
       </c>
       <c r="M16" s="0">
-        <v>0.051999999999999998</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="17">
@@ -854,40 +884,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>59271147654</v>
+        <v>34436508268</v>
       </c>
       <c r="C17" s="0">
-        <v>68999392406</v>
+        <v>40767585881</v>
       </c>
       <c r="D17" s="0">
-        <v>722204</v>
+        <v>391244</v>
       </c>
       <c r="E17" s="0">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="F17" s="0">
-        <v>247645</v>
+        <v>405497</v>
       </c>
       <c r="G17" s="0">
-        <v>2.5899999999999999</v>
+        <v>3.8900000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>9.8200000000000003</v>
+        <v>7.8600000000000003</v>
       </c>
       <c r="I17" s="0">
-        <v>85.900000000000006</v>
+        <v>84.469999999999999</v>
       </c>
       <c r="J17" s="0">
-        <v>1584</v>
+        <v>683</v>
       </c>
       <c r="K17" s="0">
-        <v>4609.3400000000001</v>
+        <v>3847.5599999999999</v>
       </c>
       <c r="L17" s="0">
-        <v>26.149999999999999</v>
+        <v>26.16</v>
       </c>
       <c r="M17" s="0">
-        <v>0.063</v>
+        <v>0.076999999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -895,40 +925,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>11309401910</v>
+        <v>10161332692</v>
       </c>
       <c r="C18" s="0">
-        <v>13093772151</v>
+        <v>11583977447</v>
       </c>
       <c r="D18" s="0">
-        <v>974964</v>
+        <v>495042</v>
       </c>
       <c r="E18" s="0">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="F18" s="0">
-        <v>35009</v>
+        <v>103174</v>
       </c>
       <c r="G18" s="0">
-        <v>2.6099999999999999</v>
+        <v>4.4100000000000001</v>
       </c>
       <c r="H18" s="0">
-        <v>10.24</v>
+        <v>8.9800000000000004</v>
       </c>
       <c r="I18" s="0">
-        <v>86.370000000000005</v>
+        <v>87.719999999999999</v>
       </c>
       <c r="J18" s="0">
-        <v>1683</v>
+        <v>702</v>
       </c>
       <c r="K18" s="0">
-        <v>4817.1000000000004</v>
+        <v>4000.9200000000001</v>
       </c>
       <c r="L18" s="0">
-        <v>21.640000000000001</v>
+        <v>25.010000000000002</v>
       </c>
       <c r="M18" s="0">
-        <v>0.050999999999999997</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="19">
@@ -936,40 +966,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>53549869999</v>
+        <v>6987218327</v>
       </c>
       <c r="C19" s="0">
-        <v>66537891945</v>
+        <v>8424621080</v>
       </c>
       <c r="D19" s="0">
-        <v>1063245</v>
+        <v>258424</v>
       </c>
       <c r="E19" s="0">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="F19" s="0">
-        <v>95258</v>
+        <v>192920</v>
       </c>
       <c r="G19" s="0">
-        <v>1.52</v>
+        <v>5.9199999999999999</v>
       </c>
       <c r="H19" s="0">
-        <v>10.609999999999999</v>
+        <v>8.1500000000000004</v>
       </c>
       <c r="I19" s="0">
-        <v>80.480000000000004</v>
+        <v>82.939999999999998</v>
       </c>
       <c r="J19" s="0">
-        <v>3245</v>
+        <v>391</v>
       </c>
       <c r="K19" s="0">
-        <v>6242.0699999999997</v>
+        <v>3413.9000000000001</v>
       </c>
       <c r="L19" s="0">
-        <v>28.940000000000001</v>
+        <v>30.370000000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0.062</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="20">
@@ -977,40 +1007,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>16043204405</v>
+        <v>14533698448</v>
       </c>
       <c r="C20" s="0">
-        <v>19821432301</v>
+        <v>18073671347</v>
       </c>
       <c r="D20" s="0">
-        <v>1477007</v>
+        <v>414914</v>
       </c>
       <c r="E20" s="0">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="F20" s="0">
-        <v>20070</v>
+        <v>223188</v>
       </c>
       <c r="G20" s="0">
-        <v>1.5</v>
+        <v>5.1200000000000001</v>
       </c>
       <c r="H20" s="0">
-        <v>12.609999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="I20" s="0">
-        <v>80.939999999999998</v>
+        <v>80.409999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>4051</v>
+        <v>574</v>
       </c>
       <c r="K20" s="0">
-        <v>6216.2399999999998</v>
+        <v>3719.6399999999999</v>
       </c>
       <c r="L20" s="0">
-        <v>25.5</v>
+        <v>26.370000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.052999999999999999</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="21">
@@ -1018,40 +1048,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>18561922198</v>
+        <v>2765483281</v>
       </c>
       <c r="C21" s="0">
-        <v>22838954562</v>
+        <v>3574947114</v>
       </c>
       <c r="D21" s="0">
-        <v>1602734</v>
+        <v>366286</v>
       </c>
       <c r="E21" s="0">
-        <v>275</v>
+        <v>129</v>
       </c>
       <c r="F21" s="0">
-        <v>22835</v>
+        <v>43197</v>
       </c>
       <c r="G21" s="0">
-        <v>1.6000000000000001</v>
+        <v>4.4299999999999997</v>
       </c>
       <c r="H21" s="0">
-        <v>12.529999999999999</v>
+        <v>8.0099999999999998</v>
       </c>
       <c r="I21" s="0">
-        <v>81.269999999999996</v>
+        <v>77.359999999999999</v>
       </c>
       <c r="J21" s="0">
-        <v>3707</v>
+        <v>624</v>
       </c>
       <c r="K21" s="0">
-        <v>6836.5100000000002</v>
+        <v>4339.5900000000001</v>
       </c>
       <c r="L21" s="0">
-        <v>25.289999999999999</v>
+        <v>32.759999999999998</v>
       </c>
       <c r="M21" s="0">
-        <v>0.052999999999999999</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1059,40 +1089,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>15574698070</v>
+        <v>822340122</v>
       </c>
       <c r="C22" s="0">
-        <v>18405311476</v>
+        <v>1044214470</v>
       </c>
       <c r="D22" s="0">
-        <v>1862886</v>
+        <v>237321</v>
       </c>
       <c r="E22" s="0">
-        <v>291</v>
+        <v>122</v>
       </c>
       <c r="F22" s="0">
-        <v>15422</v>
+        <v>27458</v>
       </c>
       <c r="G22" s="0">
-        <v>1.5600000000000001</v>
+        <v>6.2400000000000002</v>
       </c>
       <c r="H22" s="0">
-        <v>13.32</v>
+        <v>6.8799999999999999</v>
       </c>
       <c r="I22" s="0">
-        <v>84.620000000000005</v>
+        <v>78.75</v>
       </c>
       <c r="J22" s="0">
-        <v>4099</v>
+        <v>312</v>
       </c>
       <c r="K22" s="0">
-        <v>6992.04</v>
+        <v>3459.4000000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>24.010000000000002</v>
+        <v>28.359999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1100,40 +1130,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>7106195969</v>
+        <v>86445184147</v>
       </c>
       <c r="C23" s="0">
-        <v>8837173441</v>
+        <v>103998707085</v>
       </c>
       <c r="D23" s="0">
-        <v>1328898</v>
+        <v>553096</v>
       </c>
       <c r="E23" s="0">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="F23" s="0">
-        <v>8681</v>
+        <v>951585</v>
       </c>
       <c r="G23" s="0">
-        <v>1.3100000000000001</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="H23" s="0">
-        <v>12</v>
+        <v>10.640000000000001</v>
       </c>
       <c r="I23" s="0">
-        <v>80.409999999999997</v>
+        <v>83.120000000000005</v>
       </c>
       <c r="J23" s="0">
-        <v>4612</v>
+        <v>778</v>
       </c>
       <c r="K23" s="0">
-        <v>6416.8199999999997</v>
+        <v>3367.6700000000001</v>
       </c>
       <c r="L23" s="0">
-        <v>29.07</v>
+        <v>23.969999999999999</v>
       </c>
       <c r="M23" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="24">
@@ -1141,40 +1171,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>3524943561</v>
+        <v>134633109374</v>
       </c>
       <c r="C24" s="0">
-        <v>4190482296</v>
+        <v>157905146850</v>
       </c>
       <c r="D24" s="0">
-        <v>1575369</v>
+        <v>687261</v>
       </c>
       <c r="E24" s="0">
-        <v>252</v>
+        <v>162</v>
       </c>
       <c r="F24" s="0">
-        <v>3180</v>
+        <v>791519</v>
       </c>
       <c r="G24" s="0">
-        <v>1.2</v>
+        <v>3.4399999999999999</v>
       </c>
       <c r="H24" s="0">
-        <v>12.18</v>
+        <v>10.699999999999999</v>
       </c>
       <c r="I24" s="0">
-        <v>84.120000000000005</v>
+        <v>85.260000000000005</v>
       </c>
       <c r="J24" s="0">
-        <v>5229</v>
+        <v>1231</v>
       </c>
       <c r="K24" s="0">
-        <v>6779.7200000000003</v>
+        <v>3703.23</v>
       </c>
       <c r="L24" s="0">
-        <v>26.899999999999999</v>
+        <v>22.859999999999999</v>
       </c>
       <c r="M24" s="0">
-        <v>0.051999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="25">
@@ -1182,40 +1212,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>66432438526</v>
+        <v>39369944814</v>
       </c>
       <c r="C25" s="0">
-        <v>80424179428</v>
+        <v>45423124151</v>
       </c>
       <c r="D25" s="0">
-        <v>1582530</v>
+        <v>796757</v>
       </c>
       <c r="E25" s="0">
-        <v>271</v>
+        <v>174</v>
       </c>
       <c r="F25" s="0">
-        <v>58878</v>
+        <v>193384</v>
       </c>
       <c r="G25" s="0">
-        <v>1.1599999999999999</v>
+        <v>3.3900000000000001</v>
       </c>
       <c r="H25" s="0">
-        <v>11.720000000000001</v>
+        <v>11.289999999999999</v>
       </c>
       <c r="I25" s="0">
-        <v>82.599999999999994</v>
+        <v>86.670000000000002</v>
       </c>
       <c r="J25" s="0">
-        <v>5079</v>
+        <v>1350</v>
       </c>
       <c r="K25" s="0">
-        <v>8840.6100000000006</v>
+        <v>3676.9899999999998</v>
       </c>
       <c r="L25" s="0">
-        <v>32.869999999999997</v>
+        <v>21.140000000000001</v>
       </c>
       <c r="M25" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="26">
@@ -1223,40 +1253,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>9876672620</v>
+        <v>15459918486</v>
       </c>
       <c r="C26" s="0">
-        <v>12463211572</v>
+        <v>17402963694</v>
       </c>
       <c r="D26" s="0">
-        <v>1941310</v>
+        <v>843985</v>
       </c>
       <c r="E26" s="0">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F26" s="0">
-        <v>8624</v>
+        <v>70366</v>
       </c>
       <c r="G26" s="0">
-        <v>1.3400000000000001</v>
+        <v>3.4100000000000001</v>
       </c>
       <c r="H26" s="0">
-        <v>12.640000000000001</v>
+        <v>11.380000000000001</v>
       </c>
       <c r="I26" s="0">
-        <v>79.25</v>
+        <v>88.829999999999998</v>
       </c>
       <c r="J26" s="0">
-        <v>4664</v>
+        <v>1372</v>
       </c>
       <c r="K26" s="0">
-        <v>10326.940000000001</v>
+        <v>3828.27</v>
       </c>
       <c r="L26" s="0">
-        <v>33.32</v>
+        <v>21.239999999999998</v>
       </c>
       <c r="M26" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="27">
@@ -1264,40 +1294,450 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>745173672189</v>
+        <v>59271147654</v>
       </c>
       <c r="C27" s="0">
-        <v>886951733709</v>
+        <v>68999392406</v>
       </c>
       <c r="D27" s="0">
-        <v>562754</v>
+        <v>722204</v>
       </c>
       <c r="E27" s="0">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="F27" s="0">
-        <v>5643209</v>
+        <v>247645</v>
       </c>
       <c r="G27" s="0">
-        <v>3.5800000000000001</v>
+        <v>2.5899999999999999</v>
       </c>
       <c r="H27" s="0">
-        <v>9.3699999999999992</v>
+        <v>9.8200000000000003</v>
       </c>
       <c r="I27" s="0">
-        <v>84.019999999999996</v>
+        <v>85.900000000000006</v>
       </c>
       <c r="J27" s="0">
-        <v>993</v>
+        <v>1584</v>
       </c>
       <c r="K27" s="0">
-        <v>3654.79</v>
+        <v>4609.3400000000001</v>
       </c>
       <c r="L27" s="0">
-        <v>24.390000000000001</v>
+        <v>26.149999999999999</v>
       </c>
       <c r="M27" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>11309401910</v>
+      </c>
+      <c r="C28" s="0">
+        <v>13093772151</v>
+      </c>
+      <c r="D28" s="0">
+        <v>974964</v>
+      </c>
+      <c r="E28" s="0">
+        <v>224</v>
+      </c>
+      <c r="F28" s="0">
+        <v>35009</v>
+      </c>
+      <c r="G28" s="0">
+        <v>2.6099999999999999</v>
+      </c>
+      <c r="H28" s="0">
+        <v>10.24</v>
+      </c>
+      <c r="I28" s="0">
+        <v>86.370000000000005</v>
+      </c>
+      <c r="J28" s="0">
+        <v>1683</v>
+      </c>
+      <c r="K28" s="0">
+        <v>4817.1000000000004</v>
+      </c>
+      <c r="L28" s="0">
+        <v>21.640000000000001</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.050999999999999997</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>53549869999</v>
+      </c>
+      <c r="C29" s="0">
+        <v>66537891945</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1063245</v>
+      </c>
+      <c r="E29" s="0">
+        <v>220</v>
+      </c>
+      <c r="F29" s="0">
+        <v>95258</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.52</v>
+      </c>
+      <c r="H29" s="0">
+        <v>10.609999999999999</v>
+      </c>
+      <c r="I29" s="0">
+        <v>80.480000000000004</v>
+      </c>
+      <c r="J29" s="0">
+        <v>3245</v>
+      </c>
+      <c r="K29" s="0">
+        <v>6242.0699999999997</v>
+      </c>
+      <c r="L29" s="0">
+        <v>28.940000000000001</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>16043204405</v>
+      </c>
+      <c r="C30" s="0">
+        <v>19821432301</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1477007</v>
+      </c>
+      <c r="E30" s="0">
+        <v>244</v>
+      </c>
+      <c r="F30" s="0">
+        <v>20070</v>
+      </c>
+      <c r="G30" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="0">
+        <v>12.609999999999999</v>
+      </c>
+      <c r="I30" s="0">
+        <v>80.939999999999998</v>
+      </c>
+      <c r="J30" s="0">
+        <v>4051</v>
+      </c>
+      <c r="K30" s="0">
+        <v>6216.2399999999998</v>
+      </c>
+      <c r="L30" s="0">
+        <v>25.5</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.052999999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>18561922198</v>
+      </c>
+      <c r="C31" s="0">
+        <v>22838954562</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1602734</v>
+      </c>
+      <c r="E31" s="0">
+        <v>275</v>
+      </c>
+      <c r="F31" s="0">
+        <v>22835</v>
+      </c>
+      <c r="G31" s="0">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="H31" s="0">
+        <v>12.529999999999999</v>
+      </c>
+      <c r="I31" s="0">
+        <v>81.269999999999996</v>
+      </c>
+      <c r="J31" s="0">
+        <v>3707</v>
+      </c>
+      <c r="K31" s="0">
+        <v>6836.5100000000002</v>
+      </c>
+      <c r="L31" s="0">
+        <v>25.289999999999999</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.052999999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>15574698070</v>
+      </c>
+      <c r="C32" s="0">
+        <v>18405311476</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1862886</v>
+      </c>
+      <c r="E32" s="0">
+        <v>291</v>
+      </c>
+      <c r="F32" s="0">
+        <v>15422</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.5600000000000001</v>
+      </c>
+      <c r="H32" s="0">
+        <v>13.32</v>
+      </c>
+      <c r="I32" s="0">
+        <v>84.620000000000005</v>
+      </c>
+      <c r="J32" s="0">
+        <v>4099</v>
+      </c>
+      <c r="K32" s="0">
+        <v>6992.04</v>
+      </c>
+      <c r="L32" s="0">
+        <v>24.010000000000002</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>7106195969</v>
+      </c>
+      <c r="C33" s="0">
+        <v>8837173441</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1328898</v>
+      </c>
+      <c r="E33" s="0">
+        <v>221</v>
+      </c>
+      <c r="F33" s="0">
+        <v>8681</v>
+      </c>
+      <c r="G33" s="0">
+        <v>1.3100000000000001</v>
+      </c>
+      <c r="H33" s="0">
+        <v>12</v>
+      </c>
+      <c r="I33" s="0">
+        <v>80.409999999999997</v>
+      </c>
+      <c r="J33" s="0">
+        <v>4612</v>
+      </c>
+      <c r="K33" s="0">
+        <v>6416.8199999999997</v>
+      </c>
+      <c r="L33" s="0">
+        <v>29.07</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.058000000000000003</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>3524943561</v>
+      </c>
+      <c r="C34" s="0">
+        <v>4190482296</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1575369</v>
+      </c>
+      <c r="E34" s="0">
+        <v>252</v>
+      </c>
+      <c r="F34" s="0">
+        <v>3180</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="H34" s="0">
+        <v>12.18</v>
+      </c>
+      <c r="I34" s="0">
+        <v>84.120000000000005</v>
+      </c>
+      <c r="J34" s="0">
+        <v>5229</v>
+      </c>
+      <c r="K34" s="0">
+        <v>6779.7200000000003</v>
+      </c>
+      <c r="L34" s="0">
+        <v>26.899999999999999</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.051999999999999998</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>66432438526</v>
+      </c>
+      <c r="C35" s="0">
+        <v>80424179428</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1582530</v>
+      </c>
+      <c r="E35" s="0">
+        <v>271</v>
+      </c>
+      <c r="F35" s="0">
+        <v>58878</v>
+      </c>
+      <c r="G35" s="0">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H35" s="0">
+        <v>11.720000000000001</v>
+      </c>
+      <c r="I35" s="0">
+        <v>82.599999999999994</v>
+      </c>
+      <c r="J35" s="0">
+        <v>5079</v>
+      </c>
+      <c r="K35" s="0">
+        <v>8840.6100000000006</v>
+      </c>
+      <c r="L35" s="0">
+        <v>32.869999999999997</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.065000000000000002</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
+        <v>9876672620</v>
+      </c>
+      <c r="C36" s="0">
+        <v>12463211572</v>
+      </c>
+      <c r="D36" s="0">
+        <v>1941310</v>
+      </c>
+      <c r="E36" s="0">
+        <v>310</v>
+      </c>
+      <c r="F36" s="0">
+        <v>8624</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1.3400000000000001</v>
+      </c>
+      <c r="H36" s="0">
+        <v>12.640000000000001</v>
+      </c>
+      <c r="I36" s="0">
+        <v>79.25</v>
+      </c>
+      <c r="J36" s="0">
+        <v>4664</v>
+      </c>
+      <c r="K36" s="0">
+        <v>10326.940000000001</v>
+      </c>
+      <c r="L36" s="0">
+        <v>33.32</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
+        <v>812003367981</v>
+      </c>
+      <c r="C37" s="0">
+        <v>967215471843</v>
+      </c>
+      <c r="D37" s="0">
+        <v>532514</v>
+      </c>
+      <c r="E37" s="0">
+        <v>127</v>
+      </c>
+      <c r="F37" s="0">
+        <v>6780685</v>
+      </c>
+      <c r="G37" s="0">
+        <v>3.73</v>
+      </c>
+      <c r="H37" s="0">
+        <v>9.1899999999999995</v>
+      </c>
+      <c r="I37" s="0">
+        <v>83.950000000000003</v>
+      </c>
+      <c r="J37" s="0">
+        <v>915</v>
+      </c>
+      <c r="K37" s="0">
+        <v>3602.7600000000002</v>
+      </c>
+      <c r="L37" s="0">
+        <v>24.469999999999999</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.062</v>
       </c>
     </row>
   </sheetData>
